--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_45.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_45.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>DV</t>
+          <t>ExamPass?</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>SelfConfidence</t>
+          <t>HoursSleep</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.7440218730699903</v>
+        <v>0.06173270318467411</v>
       </c>
       <c r="C2">
-        <v>0.9639437435608675</v>
+        <v>-0.1948597582202213</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.4203509067351587</v>
+        <v>-1.118854040066567</v>
       </c>
       <c r="C3">
-        <v>0.1289968695496204</v>
+        <v>-0.8444412879023999</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>0.201533923758316</v>
+        <v>0.5321654277304684</v>
       </c>
       <c r="C4">
-        <v>-2.026662642976401</v>
+        <v>-0.8843010221803143</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>-0.4100286726474802</v>
+        <v>-0.2610819799389703</v>
       </c>
       <c r="C5">
-        <v>-0.5139122468539369</v>
+        <v>-0.6739830039035805</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.2557501309888841</v>
+        <v>-0.602366357703477</v>
       </c>
       <c r="C6">
-        <v>0.5800560859121777</v>
+        <v>0.08037339679617056</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.4439297598625061</v>
+        <v>1.837239942312323</v>
       </c>
       <c r="C7">
-        <v>-0.7018207954034641</v>
+        <v>0.04202452444227933</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.8201604743426423</v>
+        <v>0.3983241610052748</v>
       </c>
       <c r="C8">
-        <v>2.317718161607457</v>
+        <v>-0.2144845007306045</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>-0.4488604811480759</v>
+        <v>0.8510167154211982</v>
       </c>
       <c r="C9">
-        <v>0.6723666143142464</v>
+        <v>0.2751954401084977</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>-1.150260548731067</v>
+        <v>0.3445657248563362</v>
       </c>
       <c r="C10">
-        <v>0.257352857225716</v>
+        <v>0.6409685971527841</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>-0.7786998499718922</v>
+        <v>-0.3323563971639083</v>
       </c>
       <c r="C11">
-        <v>-0.3352787438588936</v>
+        <v>-1.342129991966641</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.9844137249242794</v>
+        <v>1.355191327787834</v>
       </c>
       <c r="C12">
-        <v>-1.550637841705219</v>
+        <v>-1.740343416662839</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.1563125286344265</v>
+        <v>0.9125822511157035</v>
       </c>
       <c r="C13">
-        <v>-1.044346837071754</v>
+        <v>1.201811564736171</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>0.705489018958995</v>
+        <v>-0.2141159805403263</v>
       </c>
       <c r="C14">
-        <v>0.6298917382560661</v>
+        <v>-0.3346454093479212</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>0.4473669759113886</v>
+        <v>0.1974716010990243</v>
       </c>
       <c r="C15">
-        <v>-0.5775659892637282</v>
+        <v>0.6892821957098448</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>-0.9101947050515018</v>
+        <v>-0.4346741655853111</v>
       </c>
       <c r="C16">
-        <v>0.03056905544537442</v>
+        <v>0.1668546257021016</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-2.642578161098386E-05</v>
+        <v>-1.319579925064462</v>
       </c>
       <c r="C17">
-        <v>-0.6947275923043607</v>
+        <v>0.8115080776353647</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.3814964233354709</v>
+        <v>-1.105673019635695</v>
       </c>
       <c r="C18">
-        <v>-0.5766014698189886</v>
+        <v>1.743715473302605</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.9321649680066507</v>
+        <v>-0.1588303367200099</v>
       </c>
       <c r="C19">
-        <v>0.2313519334720738</v>
+        <v>1.541931394089636</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.7096974711316151</v>
+        <v>1.354082347743007</v>
       </c>
       <c r="C20">
-        <v>-0.2675051195135059</v>
+        <v>-0.7648903893821376</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.4521018828807042</v>
+        <v>-0.1966222739783265</v>
       </c>
       <c r="C21">
-        <v>-0.09414370481001746</v>
+        <v>1.848109308001397</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>0.08625167649427551</v>
+        <v>-1.042332919448743</v>
       </c>
       <c r="C22">
-        <v>0.4020946889098794</v>
+        <v>-1.036278856685239</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>-0.2357905473734691</v>
+        <v>0.5336617773713112</v>
       </c>
       <c r="C23">
-        <v>-0.04340745856364842</v>
+        <v>1.469739179330543</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-1.594163448333911</v>
+        <v>-0.3490347712469943</v>
       </c>
       <c r="C24">
-        <v>-0.2579273012556496</v>
+        <v>-1.425682835392906</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.5864108774244317</v>
+        <v>0.5541929254383872</v>
       </c>
       <c r="C25">
-        <v>0.428119831631671</v>
+        <v>-1.23026116039444</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>1.101273807361193</v>
+        <v>-2.093920940878418</v>
       </c>
       <c r="C26">
-        <v>-1.006838936442202</v>
+        <v>1.65983433385929</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>-1.209838885935905</v>
+        <v>-0.8233569327392958</v>
       </c>
       <c r="C27">
-        <v>-1.302316779163303</v>
+        <v>-0.3186886574201172</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>-0.8689099981188937</v>
+        <v>-1.461759811355212</v>
       </c>
       <c r="C28">
-        <v>0.8655603331815047</v>
+        <v>0.895756760128565</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.4831908318617706</v>
+        <v>-0.7369498736283244</v>
       </c>
       <c r="C29">
-        <v>-1.171518183152915</v>
+        <v>0.3245531971860612</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.06116666357492136</v>
+        <v>-0.2794392434946754</v>
       </c>
       <c r="C30">
-        <v>1.059624708139331</v>
+        <v>0.2062859521974221</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.328034778147788</v>
+        <v>-0.666558777170895</v>
       </c>
       <c r="C31">
-        <v>0.9007597945280329</v>
+        <v>-0.3810326235724156</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.209681378713427</v>
+        <v>1.449549500463088</v>
       </c>
       <c r="C32">
-        <v>-0.5958122817735561</v>
+        <v>-0.7836098024787883</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.4390910157858843</v>
+        <v>1.060187406402753</v>
       </c>
       <c r="C33">
-        <v>0.5648144384895986</v>
+        <v>-0.006787601260723031</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>1.811846944940701</v>
+        <v>1.137283099527435</v>
       </c>
       <c r="C34">
-        <v>0.3591618171003874</v>
+        <v>-1.303522028929528</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.089804724962415</v>
+        <v>-0.2878850119975414</v>
       </c>
       <c r="C35">
-        <v>0.8258249936614586</v>
+        <v>-0.2283458771087118</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-0.9249246275577748</v>
+        <v>-0.8643772691646595</v>
       </c>
       <c r="C36">
-        <v>-0.3636586895640431</v>
+        <v>-0.17406560843227</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-0.3947427188282956</v>
+        <v>-0.1245756471158286</v>
       </c>
       <c r="C37">
-        <v>0.2252430680563547</v>
+        <v>-0.9259344490538731</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.6431611398411284</v>
+        <v>1.859887631718187</v>
       </c>
       <c r="C38">
-        <v>1.362837829523356</v>
+        <v>-0.3369371480249966</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.502150938348001</v>
+        <v>1.070585645988023</v>
       </c>
       <c r="C39">
-        <v>-0.5531922298248028</v>
+        <v>-0.1486928839609633</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-0.6613728343519227</v>
+        <v>-0.1760174986413342</v>
       </c>
       <c r="C40">
-        <v>-0.05119838102130472</v>
+        <v>-1.304781303484599</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-3.243961158532497</v>
+        <v>-1.583594476520632</v>
       </c>
       <c r="C41">
-        <v>-3.9278865637616</v>
+        <v>1.095560932126731</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>-0.5094344675677841</v>
+        <v>0.3730066128722218</v>
       </c>
       <c r="C42">
-        <v>0.008511103888949129</v>
+        <v>0.328854573170198</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.4546052111991305</v>
+        <v>-0.9662654616119846</v>
       </c>
       <c r="C43">
-        <v>-0.5200294156120836</v>
+        <v>0.6438238953870441</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.2982035848535495</v>
+        <v>-1.086454739705826</v>
       </c>
       <c r="C44">
-        <v>0.4921350874986803</v>
+        <v>-0.8107408031463796</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.8850928209254333</v>
+        <v>1.335216950150178</v>
       </c>
       <c r="C45">
-        <v>1.6277947832578</v>
+        <v>-0.2999324474648764</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.370999422797633</v>
+        <v>-0.02070923836118966</v>
       </c>
       <c r="C46">
-        <v>-0.9002683622849228</v>
+        <v>-0.7681285084401862</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-0.996530665203994</v>
+        <v>-0.2882497851941148</v>
       </c>
       <c r="C47">
-        <v>0.06326386255047423</v>
+        <v>0.07206783444791365</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-1.335065359241104</v>
+        <v>-1.095332143099307</v>
       </c>
       <c r="C48">
-        <v>-1.142963038968331</v>
+        <v>0.1589588348168647</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>-0.7676016615409191</v>
+        <v>1.858675104401013</v>
       </c>
       <c r="C49">
-        <v>-1.789349839056763</v>
+        <v>-0.8353451285174135</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>1.52559487565036</v>
+        <v>0.8919019575513489</v>
       </c>
       <c r="C50">
-        <v>-1.018263881656295</v>
+        <v>0.3544648222501664</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>1.103444269131136</v>
+        <v>0.02666730196668355</v>
       </c>
       <c r="C51">
-        <v>1.21631011653843</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>-0.5630951384931264</v>
-      </c>
-      <c r="C52">
-        <v>-1.43680290204752</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>-0.3958564430662065</v>
-      </c>
-      <c r="C53">
-        <v>1.35369668503372</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>-0.5054425575457444</v>
-      </c>
-      <c r="C54">
-        <v>-0.1637116643558382</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>-0.2921626630179747</v>
-      </c>
-      <c r="C55">
-        <v>-1.485380659027411</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>1.756380609537838</v>
-      </c>
-      <c r="C56">
-        <v>-0.3612838220125352</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>0.1914744216239717</v>
-      </c>
-      <c r="C57">
-        <v>-0.1306527593308354</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>0.5564785278787725</v>
-      </c>
-      <c r="C58">
-        <v>0.4338169582328373</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>1.254970477791539</v>
-      </c>
-      <c r="C59">
-        <v>-0.5484149022216463</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>0.4654725376279146</v>
-      </c>
-      <c r="C60">
-        <v>-0.5086095743791369</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>1.366682766147348</v>
-      </c>
-      <c r="C61">
-        <v>0.7325736587035563</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>-0.06074481885669</v>
-      </c>
-      <c r="C62">
-        <v>0.6187716150221236</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>0.24477514799276</v>
-      </c>
-      <c r="C63">
-        <v>-0.966930057112491</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>-1.374690969319169</v>
-      </c>
-      <c r="C64">
-        <v>-0.3239509613879784</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>-1.005688426938334</v>
-      </c>
-      <c r="C65">
-        <v>0.7919241058716557</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>-0.5644224834726133</v>
-      </c>
-      <c r="C66">
-        <v>-0.1692408651723306</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>-0.6578474928387449</v>
-      </c>
-      <c r="C67">
-        <v>0.5982645049988973</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>0.8980878504495864</v>
-      </c>
-      <c r="C68">
-        <v>1.242295541557185</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>0.5154709299499434</v>
-      </c>
-      <c r="C69">
-        <v>0.2688194818448905</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>-1.16046992727281</v>
-      </c>
-      <c r="C70">
-        <v>-1.181128576050439</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>-0.2495441558491658</v>
-      </c>
-      <c r="C71">
-        <v>0.7208610889602404</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>-0.1085661295625522</v>
-      </c>
-      <c r="C72">
-        <v>0.2383737832212091</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>-1.118516850295758</v>
-      </c>
-      <c r="C73">
-        <v>-0.2758666568561412</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>-0.2839004427678788</v>
-      </c>
-      <c r="C74">
-        <v>0.2113067845800651</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>1.184764279274117</v>
-      </c>
-      <c r="C75">
-        <v>-1.038457687931089</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>0.5991355555223045</v>
-      </c>
-      <c r="C76">
-        <v>1.210779813573855</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>-1.818665469262404</v>
-      </c>
-      <c r="C77">
-        <v>-2.462520992863966</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>-0.6711525879323258</v>
-      </c>
-      <c r="C78">
-        <v>0.006853818828978231</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>-0.9507977513837057</v>
-      </c>
-      <c r="C79">
-        <v>-0.6185129452354677</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>0.32892359756873</v>
-      </c>
-      <c r="C80">
-        <v>1.010895591407021</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>-0.8923051594851125</v>
-      </c>
-      <c r="C81">
-        <v>-1.523058163120343</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>-1.139045488634138</v>
-      </c>
-      <c r="C82">
-        <v>-1.104637797685314</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>-1.025332332797924</v>
-      </c>
-      <c r="C83">
-        <v>-0.4710818387022069</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>-0.5474857861176651</v>
-      </c>
-      <c r="C84">
-        <v>0.9930983564664431</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-0.5602463589390302</v>
-      </c>
-      <c r="C85">
-        <v>-1.022392430870249</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>0.6341993692268161</v>
-      </c>
-      <c r="C86">
-        <v>0.3178777224619872</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>-0.6399471989429149</v>
-      </c>
-      <c r="C87">
-        <v>0.3756439562965024</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>-0.1546215420575411</v>
-      </c>
-      <c r="C88">
-        <v>0.4859926101322251</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>-0.5243272274809337</v>
-      </c>
-      <c r="C89">
-        <v>1.075321852224576</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>-0.5279159478397647</v>
-      </c>
-      <c r="C90">
-        <v>-1.782809364802286</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>-1.182833250437926</v>
-      </c>
-      <c r="C91">
-        <v>-1.0388298328754</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>0.2709842258886485</v>
-      </c>
-      <c r="C92">
-        <v>1.632203591460713</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>-1.598949835695742</v>
-      </c>
-      <c r="C93">
-        <v>-0.2822674883363025</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>0.9346754818096937</v>
-      </c>
-      <c r="C94">
-        <v>-1.147393319031859</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>2.060529164121239</v>
-      </c>
-      <c r="C95">
-        <v>1.259989111553791</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>1.668979074654993</v>
-      </c>
-      <c r="C96">
-        <v>0.4202053676499293</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>0.7923269075977593</v>
-      </c>
-      <c r="C97">
-        <v>0.2345109648037383</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>-0.3078243007699375</v>
-      </c>
-      <c r="C98">
-        <v>0.09066601175901196</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>-0.8993713095816124</v>
-      </c>
-      <c r="C99">
-        <v>0.3488062290933792</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>0.1707239774138949</v>
-      </c>
-      <c r="C100">
-        <v>-1.71073461231376</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>0.06386702934416334</v>
-      </c>
-      <c r="C101">
-        <v>-0.8714817571786359</v>
+        <v>-0.08718953186369893</v>
       </c>
     </row>
   </sheetData>
